--- a/data/用例.xlsx
+++ b/data/用例.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\jkzdh封装\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04076D63-E25A-4A25-8CDB-6BAAE4F33769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1E7D5A-6273-450A-AEF1-43FC58C94D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6060" yWindow="2856" windowWidth="23772" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7620" yWindow="1392" windowWidth="23772" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case1" sheetId="2" r:id="rId1"/>
@@ -3867,7 +3867,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
-        <v>101</v>
+        <v>400</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>41</v>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
-        <v>102</v>
+        <v>401</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>41</v>
@@ -3951,7 +3951,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
-        <v>103</v>
+        <v>402</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>41</v>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
-        <v>104</v>
+        <v>403</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>41</v>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
-        <v>105</v>
+        <v>404</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>41</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
-        <v>106</v>
+        <v>405</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>41</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
-        <v>107</v>
+        <v>406</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>41</v>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
-        <v>108</v>
+        <v>407</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>41</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
-        <v>109</v>
+        <v>408</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>41</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
-        <v>110</v>
+        <v>409</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>41</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
-        <v>111</v>
+        <v>410</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>36</v>
@@ -4325,7 +4325,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
-        <v>221</v>
+        <v>411</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>41</v>

--- a/data/用例.xlsx
+++ b/data/用例.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\jkzdh封装\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1E7D5A-6273-450A-AEF1-43FC58C94D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5776C9AD-8541-4709-9857-9D747D268909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7620" yWindow="1392" windowWidth="23772" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="336" yWindow="1968" windowWidth="28044" windowHeight="12900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case1" sheetId="2" r:id="rId1"/>
-    <sheet name="case2" sheetId="3" r:id="rId2"/>
-    <sheet name="case3" sheetId="4" r:id="rId3"/>
+    <sheet name="case4" sheetId="5" r:id="rId2"/>
+    <sheet name="case2" sheetId="3" r:id="rId3"/>
+    <sheet name="case3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="276">
   <si>
     <t>编号</t>
   </si>
@@ -962,6 +963,22 @@
   </si>
   <si>
     <t>分页查询-页码为0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>J-001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择用户账号登录成功</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/login</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"username":"admin","password":"admin123"}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2460,6 +2477,168 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB8860D-2917-4979-9EB9-E96916DE0F4D}">
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F3" t="s">
+        <v>274</v>
+      </c>
+      <c r="I3" t="s">
+        <v>275</v>
+      </c>
+      <c r="L3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M3">
+        <v>200</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C23BA289-1AB2-475C-82BC-A401925074A6}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3732,7 +3911,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D34147-C5F0-4558-B31E-11600D74D284}">
   <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>

--- a/data/用例.xlsx
+++ b/data/用例.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\jkzdh封装\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5776C9AD-8541-4709-9857-9D747D268909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEAB51BC-3485-417A-8154-F5439C7CDA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="1968" windowWidth="28044" windowHeight="12900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5916" yWindow="4644" windowWidth="28044" windowHeight="11412" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case1" sheetId="2" r:id="rId1"/>
-    <sheet name="case4" sheetId="5" r:id="rId2"/>
-    <sheet name="case2" sheetId="3" r:id="rId3"/>
-    <sheet name="case3" sheetId="4" r:id="rId4"/>
+    <sheet name="case2" sheetId="3" r:id="rId2"/>
+    <sheet name="case3" sheetId="4" r:id="rId3"/>
+    <sheet name="case4" sheetId="5" r:id="rId4"/>
+    <sheet name="case5" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="382">
   <si>
     <t>编号</t>
   </si>
@@ -966,19 +967,419 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>post</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/teacher/score/update</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>$..code</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>J-001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>选择用户账号登录成功</t>
+    <t>J-002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>session</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>会话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Authorization":"Bearer {{token}}"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>session_teacher</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>session_student</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库预期结果</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT score from score WHERE student_id=4 AND course_id=1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>J-003</t>
+  </si>
+  <si>
+    <t>正向登录</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理员登录成功</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>/student-system/login</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"username":"admin","password":"admin123"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常登录</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>密码错误</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"username":"admin","password":"1293217483204738492"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名为空</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"username":"","password":"admin123"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>垂直越权</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老师修改学生成绩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>学生调用管理员新增班级接口</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/admin/class/save</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"studentid":"7","courseid":"2","score":"99","remark":"TEST_测试备注"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"className":"TEST_测试1班","classCode":"shell123","description":"开开心心每一天"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>越权</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>垂直越权</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>学生调用老师编辑成绩接口</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>越权</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平越权</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老师A修改老师B的课程成绩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"id": 4, "studentId": 6, "courseId":4, "score": 66.5, "remark": "水平越权尝试"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{b_score}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"b_score":"SELECT score from score WHERE student_id=6 ;"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据一致性</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>双重断言</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常处理</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>边界值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>成绩设为-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"id": 1, "studentId": 4, "courseId":1, "score": 99.5, "remark": "测试1"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新不存在的成绩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"id": 2, "studentId": 4, "courseId":3, "score": -1, "remark": "测试边界值"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"id": 999, "studentId": 4, "courseId":3, "score": 99, "remark": "测试不存在成绩"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>J-004</t>
+  </si>
+  <si>
+    <t>J-005</t>
+  </si>
+  <si>
+    <t>J-006</t>
+  </si>
+  <si>
+    <t>J-007</t>
+  </si>
+  <si>
+    <t>J-008</t>
+  </si>
+  <si>
+    <t>J-009</t>
+  </si>
+  <si>
+    <t>SELECT score from score WHERE student_id=6 AND id=4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>教室新增学生成绩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/teacher/score/save</t>
+  </si>
+  <si>
+    <t>教师修改成绩为95</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>老师查询成绩看是否修改成功</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>get</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/teacher/score/list</t>
+  </si>
+  <si>
+    <t>{"id":"{{ID_score}}"}</t>
+  </si>
+  <si>
+    <t>{"api_score": "$.data[0].score"}</t>
+  </si>
+  <si>
+    <t>老师删除学生成绩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/teacher/score/delete</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	SELECT count(*) FROM score WHERE id={{ID_score}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT score FROM score WHERE id={{ID_score}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{api_score}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"ID_score": "SELECT id FROM score WHERE student_id=4 AND course_id=3"}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"studentId":"4","courseId":"3","score":"88.3","remark":"TEST_新增成绩"}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"id":"{{ID_score}}","studentId":"4","courseId":"3","score":"95.6","remark":"TEST_新增成绩"}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"courseId":3}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L-101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L-102</t>
+  </si>
+  <si>
+    <t>L-103</t>
+  </si>
+  <si>
+    <t>L-104</t>
+  </si>
+  <si>
+    <t>L-105</t>
+  </si>
+  <si>
+    <t>post</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/admin/class/save</t>
+  </si>
+  <si>
+    <t>session_admin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"ID_class": "SELECT id FROM class WHERE class_code='TEST_800'"}</t>
+  </si>
+  <si>
+    <t>管理员给student1分配班级</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/admin/student/update</t>
+  </si>
+  <si>
+    <t>{"id":4,"username":"student1","name":"张三","classId":"{{ID_class}}"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>链路1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理员新增班级</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理员把课程分配给teacher1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>POST</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/admin/course/save</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"courseName":"测试课程","courseCode":"CS123","teacherId":"2","classId":{{ID_class}},"semester":"2026-2027-1","description":"测试课程"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老师给student1增加成绩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"ID_course":"SELECT id FROM course WHERE class_id={{ID_class}} AND course_name='测试课程' "}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老师将student1加入课程</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"courseId":"{{ID_course}}","studentId":"4"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/teacher/course/select</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"studentId":4,"courseId":{{ID_course}},"score":"88.8","remark":"链路1新增测试成绩"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>student1查询新增课程的成绩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>get</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>/student-system/student/score/list</t>
+  </si>
+  <si>
+    <t>SELECT score FROM score WHERE student_id=4 AND course_id={{ID_course}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L-106</t>
+  </si>
+  <si>
+    <t>L-107</t>
+  </si>
+  <si>
+    <t>L-108</t>
+  </si>
+  <si>
+    <t>L-109</t>
+  </si>
+  <si>
+    <t>L-110</t>
+  </si>
+  <si>
+    <t>{"className":"TEST_链路班","classCode":"TEST_800","description":"TEST_链路"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>链路2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>链路2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>增删改查</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨角色资源流转</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT count(*) FROM student_course WHERE course_id={{ID_course}} AND student_id=4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sql提取</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -986,7 +1387,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1018,14 +1419,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
       <family val="3"/>
@@ -1046,23 +1439,38 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1089,8 +1497,20 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1098,11 +1518,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1121,25 +1556,52 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1482,7 +1944,7 @@
     <col min="18" max="18" width="8.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1538,7 +2000,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -1594,645 +2056,645 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7" t="s">
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7" t="s">
+      <c r="K3" s="6"/>
+      <c r="L3" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="Q3" s="6"/>
+      <c r="R3" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7" t="s">
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7" t="s">
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7" t="s">
+      <c r="K5" s="6"/>
+      <c r="L5" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7" t="s">
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="O6" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7" t="s">
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7" t="s">
+      <c r="K7" s="6"/>
+      <c r="L7" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="O7" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="Q7" s="6"/>
+      <c r="R7" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7" t="s">
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7" t="s">
+      <c r="K8" s="6"/>
+      <c r="L8" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="O8" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7" t="s">
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7" t="s">
+      <c r="K9" s="6"/>
+      <c r="L9" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="O9" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="P9" s="7"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7" t="s">
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="6"/>
+      <c r="L10" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7" t="s">
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="6"/>
+      <c r="L11" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="O11" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="P11" s="7" t="s">
+      <c r="P11" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="Q11" s="6"/>
+      <c r="R11" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7" t="s">
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7" t="s">
+      <c r="K12" s="6"/>
+      <c r="L12" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="O12" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7" t="s">
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="M13" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="N13" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
         <v>12</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7" t="s">
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="6"/>
+      <c r="L14" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="M14" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="N14" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="O14" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="P14" s="7" t="s">
+      <c r="P14" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="Q14" s="6"/>
+      <c r="R14" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7">
         <v>13</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7" t="s">
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="N15" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="O15" s="7" t="s">
+      <c r="O15" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7">
         <v>14</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7" t="s">
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="N16" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="O16" s="7" t="s">
+      <c r="O16" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="8" t="b">
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2477,168 +2939,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB8860D-2917-4979-9EB9-E96916DE0F4D}">
-  <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I3" t="s">
-        <v>275</v>
-      </c>
-      <c r="L3" t="s">
-        <v>177</v>
-      </c>
-      <c r="M3">
-        <v>200</v>
-      </c>
-      <c r="R3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C23BA289-1AB2-475C-82BC-A401925074A6}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2777,1127 +3077,1077 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+    <row r="3" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16">
         <v>200</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J3" s="11" t="s">
+      <c r="G3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="K3" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L3" s="11" t="s">
+      <c r="K3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L3" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="Q3" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R3" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="Q3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R3" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
         <v>201</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J4" s="11" t="s">
+      <c r="G4" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J4" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="K4" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L4" s="11" t="s">
+      <c r="K4" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L4" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R4" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R4" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16">
         <v>202</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J5" s="11" t="s">
+      <c r="G5" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J5" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="K5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L5" s="11" t="s">
+      <c r="K5" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="P5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R5" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+      <c r="P5" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R5" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16">
         <v>203</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J6" s="11" t="s">
+      <c r="G6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="11" t="s">
+      <c r="K6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="N6" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="P6" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q6" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R6" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+      <c r="N6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
         <v>204</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="18">
         <v>400</v>
       </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+      <c r="R7" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="16">
         <v>205</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="18">
         <v>400</v>
       </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+      <c r="R8" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
         <v>206</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L9" s="11" t="s">
+      <c r="G9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="P9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R9" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+      <c r="N9" s="17"/>
+      <c r="O9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R9" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16">
         <v>207</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="11" t="s">
+      <c r="H10" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="N10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R10" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+      <c r="N10" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="O10" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P10" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R10" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="16">
         <v>208</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="18">
         <v>401</v>
       </c>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+      <c r="R11" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16">
         <v>209</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J12" s="11" t="s">
+      <c r="H12" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="K12" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L12" s="11" t="s">
+      <c r="K12" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="N12" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="O12" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q12" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R12" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+      <c r="N12" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="O12" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P12" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R12" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
         <v>210</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J13" s="11" t="s">
+      <c r="H13" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="K13" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L13" s="11" t="s">
+      <c r="K13" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="N13" s="11" t="s">
+      <c r="N13" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="P13" s="11" t="s">
+      <c r="P13" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="Q13" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R13" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+      <c r="Q13" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R13" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16">
         <v>211</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H14" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J14" s="11" t="s">
+      <c r="H14" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="K14" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L14" s="11" t="s">
+      <c r="K14" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="Q14" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R14" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+      <c r="Q14" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R14" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="16">
         <v>212</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L15" s="11" t="s">
+      <c r="H15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="M15" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="N15" s="11" t="s">
+      <c r="N15" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="O15" s="11" t="s">
+      <c r="O15" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="P15" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q15" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R15" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+      <c r="P15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R15" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="16">
         <v>213</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J16" s="11" t="s">
+      <c r="H16" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J16" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="K16" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L16" s="11" t="s">
+      <c r="K16" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L16" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M16" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="N16" s="11" t="s">
+      <c r="N16" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="P16" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q16" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R16" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+      <c r="P16" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R16" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="16">
         <v>214</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="18">
         <v>400</v>
       </c>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+      <c r="R17" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="16">
         <v>215</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L18" s="11" t="s">
+      <c r="H18" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L18" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="M18" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="N18" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="O18" s="11" t="s">
+      <c r="O18" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="P18" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q18" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R18" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+      <c r="P18" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q18" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R18" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="16">
         <v>216</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="M19" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="O19" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="P19" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q19" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R19" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="16">
+        <v>217</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="M20" s="18">
+        <v>400</v>
+      </c>
+      <c r="R20" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="16">
+        <v>218</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="M21" s="18">
+        <v>400</v>
+      </c>
+      <c r="R21" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="16">
+        <v>219</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L19" s="11" t="s">
+      <c r="H22" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L22" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M19" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="N19" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="O19" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="P19" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q19" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R19" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
-        <v>217</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20" s="11" t="s">
+      <c r="M22" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="O22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R22" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="16">
+        <v>220</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="11" t="s">
+      <c r="H23" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="L23" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="M20" s="6">
-        <v>400</v>
-      </c>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
-        <v>218</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="M21" s="6">
-        <v>400</v>
-      </c>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
-        <v>219</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="11" t="s">
+      <c r="M23" s="18">
+        <v>200</v>
+      </c>
+      <c r="N23" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="O23" s="18">
+        <v>0</v>
+      </c>
+      <c r="R23" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="16">
+        <v>221</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="N22" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="O22" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="P22" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q22" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R22" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
-        <v>220</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="M23" s="6">
-        <v>200</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="O23" s="6">
-        <v>0</v>
-      </c>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
-        <v>221</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L24" s="11" t="s">
+      <c r="G24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L24" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M24" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="N24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="O24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="P24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R24" s="10" t="b">
+      <c r="N24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="O24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R24" s="16" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3911,7 +4161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D34147-C5F0-4558-B31E-11600D74D284}">
   <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -4044,504 +4294,1474 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+    <row r="3" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16">
         <v>400</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="16" t="s">
         <v>39</v>
       </c>
+      <c r="F3" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="18">
+        <v>500</v>
+      </c>
+      <c r="R3" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
+        <v>401</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="18">
+        <v>500</v>
+      </c>
+      <c r="R4" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16">
+        <v>402</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="18">
+        <v>200</v>
+      </c>
+      <c r="R5" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16">
+        <v>403</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="18">
+        <v>500</v>
+      </c>
+      <c r="R6" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
+        <v>404</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="18">
+        <v>500</v>
+      </c>
+      <c r="R7" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="16">
+        <v>405</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="18">
+        <v>200</v>
+      </c>
+      <c r="R8" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
+        <v>406</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" s="18">
+        <v>200</v>
+      </c>
+      <c r="R9" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16">
+        <v>407</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" s="18">
+        <v>200</v>
+      </c>
+      <c r="R10" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="16">
+        <v>408</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" s="18">
+        <v>400</v>
+      </c>
+      <c r="R11" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16">
+        <v>409</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="18">
+        <v>200</v>
+      </c>
+      <c r="R12" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
+        <v>410</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" s="18">
+        <v>500</v>
+      </c>
+      <c r="R13" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16">
+        <v>411</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" s="18">
+        <v>500</v>
+      </c>
+      <c r="R14" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C70197-391A-4506-A538-3210821658F6}">
+  <dimension ref="A1:R12"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.90625" customWidth="1"/>
+    <col min="9" max="9" width="77.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="63.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="57.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.26953125" customWidth="1"/>
+    <col min="16" max="16" width="26.36328125" customWidth="1"/>
+    <col min="17" max="17" width="78.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="15" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="P1" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M3" s="9">
+        <v>200</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="R3" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M4" s="9">
+        <v>200</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="O4" s="11">
+        <v>95.6</v>
+      </c>
+      <c r="R4" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="L5" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M5" s="9">
+        <v>200</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="R5" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M6" s="9">
+        <v>200</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M7" s="9">
+        <v>200</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="R7" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M8" s="9">
+        <v>200</v>
+      </c>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M9" s="9">
+        <v>200</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="R9" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="J10" s="13"/>
+      <c r="L10" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M10" s="9">
+        <v>200</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="O10" s="9">
+        <v>1</v>
+      </c>
+      <c r="R10" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M11" s="9">
+        <v>200</v>
+      </c>
+      <c r="R11" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M12" s="9">
+        <v>200</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="O12" s="11">
+        <v>88.8</v>
+      </c>
+      <c r="R12" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:R11">
+    <sortCondition ref="B3:B11"/>
+    <sortCondition ref="C3:C11"/>
+  </sortState>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F31123F-1BB7-4602-9433-3E45F62821D2}">
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="70.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="50.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>167</v>
+      </c>
       <c r="F3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="6">
+        <v>287</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M3" s="9">
         <v>500</v>
       </c>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10" t="b">
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M4" s="9">
+        <v>500</v>
+      </c>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M5" s="9">
+        <v>200</v>
+      </c>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M6" s="9">
+        <v>200</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="O6" s="11">
+        <v>99.5</v>
+      </c>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M7" s="9">
+        <v>500</v>
+      </c>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M8" s="9">
+        <v>500</v>
+      </c>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M9" s="9">
+        <v>403</v>
+      </c>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M10" s="9">
+        <v>403</v>
+      </c>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
-        <v>401</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" s="6">
-        <v>500</v>
-      </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
-        <v>402</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" s="6">
-        <v>200</v>
-      </c>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+    <row r="11" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="M11" s="9">
         <v>403</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" s="6">
-        <v>500</v>
-      </c>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
-        <v>404</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" s="6">
-        <v>500</v>
-      </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
-        <v>405</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" s="6">
-        <v>200</v>
-      </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
-        <v>406</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M9" s="6">
-        <v>200</v>
-      </c>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
-        <v>407</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M10" s="6">
-        <v>200</v>
-      </c>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
-        <v>408</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="6">
-        <v>400</v>
-      </c>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
-        <v>409</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" s="6">
-        <v>200</v>
-      </c>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
-        <v>410</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M13" s="6">
-        <v>500</v>
-      </c>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
-        <v>411</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M14" s="6">
-        <v>500</v>
-      </c>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10" t="b">
-        <v>0</v>
+      <c r="N11" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="R11" s="9" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/用例.xlsx
+++ b/data/用例.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\jkzdh封装\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEAB51BC-3485-417A-8154-F5439C7CDA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CBDF25-21F8-473A-8D01-8F42DB6C6247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5916" yWindow="4644" windowWidth="28044" windowHeight="11412" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2436" yWindow="2688" windowWidth="28044" windowHeight="11400" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case1" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="390">
   <si>
     <t>编号</t>
   </si>
@@ -1380,6 +1380,32 @@
   </si>
   <si>
     <t>sql提取</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>REG-002</t>
+  </si>
+  <si>
+    <t>字段缺失</t>
+  </si>
+  <si>
+    <t>教师查询学生课程</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>/student-system/teacher/course/students</t>
+  </si>
+  <si>
+    <t>session_teacher</t>
+  </si>
+  <si>
+    <t>{"courseId":2}</t>
+  </si>
+  <si>
+    <t>回归用例</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1387,7 +1413,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1469,6 +1495,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1537,7 +1571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1602,6 +1636,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5252,7 +5292,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F31123F-1BB7-4602-9433-3E45F62821D2}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.81640625" bestFit="1" customWidth="1"/>
@@ -5764,6 +5804,48 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="22">
+        <v>200</v>
+      </c>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/用例.xlsx
+++ b/data/用例.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\jkzdh封装\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CBDF25-21F8-473A-8D01-8F42DB6C6247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5D3A2F-B46F-45BD-8EB4-621E9C25483B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2436" yWindow="2688" windowWidth="28044" windowHeight="11400" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="3540" windowWidth="28044" windowHeight="11400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case1" sheetId="2" r:id="rId1"/>
@@ -1194,9 +1194,6 @@
     <t>/student-system/teacher/score/list</t>
   </si>
   <si>
-    <t>{"id":"{{ID_score}}"}</t>
-  </si>
-  <si>
     <t>{"api_score": "$.data[0].score"}</t>
   </si>
   <si>
@@ -1208,30 +1205,14 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">	SELECT count(*) FROM score WHERE id={{ID_score}}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SELECT score FROM score WHERE id={{ID_score}}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>{{api_score}}</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"ID_score": "SELECT id FROM score WHERE student_id=4 AND course_id=3"}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"studentId":"4","courseId":"3","score":"88.3","remark":"TEST_新增成绩"}</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>{"id":"{{ID_score}}","studentId":"4","courseId":"3","score":"95.6","remark":"TEST_新增成绩"}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>{"courseId":3}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1407,6 +1388,26 @@
   <si>
     <t>回归用例</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"ID_course": "SELECT id FROM score WHERE student_id=4 AND course_id=3"}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"id":"{{ID_course}}","studentId":"4","courseId":"3","score":"95.6","remark":"TEST_新增成绩"}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT score FROM score WHERE id={{ID_course}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"id":"{{ID_course}}"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	SELECT count(*) FROM score WHERE id={{ID_course}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4825,7 +4826,7 @@
         <v>15</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="R1" s="20" t="s">
         <v>17</v>
@@ -4889,13 +4890,13 @@
     </row>
     <row r="3" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>325</v>
@@ -4910,7 +4911,7 @@
         <v>280</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="L3" s="9" t="s">
         <v>274</v>
@@ -4919,7 +4920,7 @@
         <v>200</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>338</v>
+        <v>385</v>
       </c>
       <c r="R3" s="9" t="b">
         <v>1</v>
@@ -4927,13 +4928,13 @@
     </row>
     <row r="4" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>327</v>
@@ -4948,7 +4949,7 @@
         <v>280</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="L4" s="9" t="s">
         <v>274</v>
@@ -4957,7 +4958,7 @@
         <v>200</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
       <c r="O4" s="11">
         <v>95.6</v>
@@ -4968,13 +4969,13 @@
     </row>
     <row r="5" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>328</v>
@@ -4989,7 +4990,7 @@
         <v>280</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="I5" s="10"/>
       <c r="L5" s="9" t="s">
@@ -4999,13 +5000,13 @@
         <v>200</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
       <c r="O5" s="13" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="R5" s="9" t="b">
         <v>1</v>
@@ -5013,28 +5014,28 @@
     </row>
     <row r="6" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>272</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>280</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>331</v>
+        <v>388</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>274</v>
@@ -5043,7 +5044,7 @@
         <v>200</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>335</v>
+        <v>389</v>
       </c>
       <c r="O6" s="11">
         <v>0</v>
@@ -5054,28 +5055,28 @@
     </row>
     <row r="7" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>274</v>
@@ -5084,7 +5085,7 @@
         <v>200</v>
       </c>
       <c r="Q7" s="10" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="R7" s="9" t="b">
         <v>1</v>
@@ -5092,28 +5093,28 @@
     </row>
     <row r="8" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>352</v>
-      </c>
       <c r="G8" s="9" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>274</v>
@@ -5128,28 +5129,28 @@
     </row>
     <row r="9" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>359</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>274</v>
@@ -5158,7 +5159,7 @@
         <v>200</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="R9" s="9" t="b">
         <v>1</v>
@@ -5166,28 +5167,28 @@
     </row>
     <row r="10" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>280</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="J10" s="13"/>
       <c r="L10" s="9" t="s">
@@ -5197,7 +5198,7 @@
         <v>200</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="O10" s="9">
         <v>1</v>
@@ -5208,19 +5209,19 @@
     </row>
     <row r="11" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>326</v>
@@ -5229,7 +5230,7 @@
         <v>280</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>274</v>
@@ -5243,22 +5244,22 @@
     </row>
     <row r="12" spans="1:18" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>379</v>
-      </c>
       <c r="D12" s="9" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>281</v>
@@ -5270,7 +5271,7 @@
         <v>200</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="O12" s="11">
         <v>88.8</v>
@@ -5806,28 +5807,28 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="H12" s="10" t="s">
         <v>383</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>388</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>

--- a/data/用例.xlsx
+++ b/data/用例.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\jkzdh封装\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5D3A2F-B46F-45BD-8EB4-621E9C25483B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D53A622-E8F8-41CE-8CF2-7EE5CCB1A44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="3540" windowWidth="28044" windowHeight="11400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="3540" windowWidth="28044" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case1" sheetId="2" r:id="rId1"/>
